--- a/UnitySamples/DataConvert/Data/Data_Game.xlsx
+++ b/UnitySamples/DataConvert/Data/Data_Game.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Project\Study\UnitySamples\DataConvert\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Project\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCF5EBED-2DAA-46DA-81F4-4C847BD5082E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB55D903-6BC4-44FC-94F5-C446AA9E5C6D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="2205" windowWidth="21000" windowHeight="12915" activeTab="1" xr2:uid="{1A085EA2-054B-4DC0-8544-BB78D87C1A04}"/>
+    <workbookView xWindow="-24285" yWindow="1320" windowWidth="21000" windowHeight="12915" xr2:uid="{1A085EA2-054B-4DC0-8544-BB78D87C1A04}"/>
   </bookViews>
   <sheets>
     <sheet name="Dungeon" sheetId="1" r:id="rId1"/>
@@ -34,54 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
-  <si>
-    <t>Index(int)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Difficult(float)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnemyList(int Array)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{1, 2, 3, 4, 5}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{2, 2, 3, 4, 5}</t>
-  </si>
-  <si>
-    <t>{3, 2, 3, 4, 5}</t>
-  </si>
-  <si>
-    <t>{4, 2, 3, 4, 5}</t>
-  </si>
-  <si>
-    <t>{5, 2, 3, 4, 5}</t>
-  </si>
-  <si>
-    <t>{6, 2, 3, 4, 5}</t>
-  </si>
-  <si>
-    <t>{7, 2, 3, 4, 5}</t>
-  </si>
-  <si>
-    <t>{8, 2, 3, 4, 5}</t>
-  </si>
-  <si>
-    <t>{9, 2, 3, 4, 5}</t>
-  </si>
-  <si>
-    <t>{10, 2, 3, 4, 5}</t>
-  </si>
-  <si>
-    <t>DungeonName(string)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Aa</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,26 +76,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>## Index : 던전의 인덱스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>## DungeonName : 던전 이름</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>## Difficult : 던전의 난이도 배수로서 사용, ex) 1 -&gt; 100% 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>## EnemyList : 던전에서 등장하는 적군 리스트, Enemy 시트 참조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name(string)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -183,11 +116,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>## Index : 적군의 인덱스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>## Name : 적군의 이름</t>
+    <t>Index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Difficult</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1, 2, 3, 4, 5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2, 2, 3, 4, 5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3, 2, 3, 4, 5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4, 2, 3, 4, 5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5, 2, 3, 4, 5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[6, 2, 3, 4, 5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[7, 2, 3, 4, 5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[8, 2, 3, 4, 5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[9, 2, 3, 4, 5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[10, 2, 3, 4, 5]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -552,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62AE373B-0A3A-47F4-BB76-F55FBA0A66E6}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -561,282 +546,266 @@
     <col min="4" max="4" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1.5</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>2.5</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>3.5</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>4.5</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>5.5</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C67268F-C59C-403E-B622-32EA233A1F52}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>